--- a/Borssele_Debt_Model.xlsx
+++ b/Borssele_Debt_Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cascornelissen/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A7D8ED0-F075-FE4C-B62B-4E45B93D56DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6812E31A-9153-074F-B710-89599E5907D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="-7680" windowWidth="38400" windowHeight="21600" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Read Me" sheetId="1" r:id="rId1"/>
@@ -41,10 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="278">
-  <si>
-    <t>Borssele 1 &amp; 2 — Project Finance Debt Model</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="272">
   <si>
     <t>Tabs</t>
   </si>
@@ -52,30 +49,15 @@
     <t>Debt sizing methodology (avoids circularity)</t>
   </si>
   <si>
-    <t>Debt is sized off the LOWEST of three tests, per market convention:</t>
-  </si>
-  <si>
     <t xml:space="preserve">  1) DSCR-sculpted capacity: initial balance = PV of the CFADS/DSCR-target debt service</t>
   </si>
   <si>
     <t xml:space="preserve">     iteration needed).</t>
   </si>
   <si>
-    <t xml:space="preserve">  2) Leverage cap: 70% of total project cost (CAPEX).</t>
-  </si>
-  <si>
     <t xml:space="preserve">  3) LLCR-implied capacity: PV of sizing CFADS at the LLCR discount rate, / LLCR minimum.</t>
   </si>
   <si>
-    <t>CFADS for the SIZING test excludes the interest tax shield (a conservative, standard</t>
-  </si>
-  <si>
-    <t>lender convention). The Cash Flow &amp; Waterfall tab computes ACTUAL tax with the interest</t>
-  </si>
-  <si>
-    <t>deduction (subject to the ATAD earnings-stripping cap), so realised DSCR normally comes</t>
-  </si>
-  <si>
     <t>Debt tenor &amp; refinancing</t>
   </si>
   <si>
@@ -88,24 +70,12 @@
     <t>shorter-tenor structure, not the base case.</t>
   </si>
   <si>
-    <t>Simplifications (documented, not hidden)</t>
-  </si>
-  <si>
-    <t>Distribution lock-up traps cash (shown) rather than dynamically re-sculpting the</t>
-  </si>
-  <si>
-    <t>LLCR is shown at financial close (the primary sizing check), not re-tested every year.</t>
-  </si>
-  <si>
     <t>Cost overrun is assumed funded by additional sponsor equity, not additional debt.</t>
   </si>
   <si>
     <t>Years 16-25 (post-debt-repayment) continue at the ex-ante price for consistency with</t>
   </si>
   <si>
-    <t>Project 1's ex-ante lens; Project 1's ex-post work already covers realised pricing.</t>
-  </si>
-  <si>
     <t>Assumptions</t>
   </si>
   <si>
@@ -361,9 +331,6 @@
     <t>ATAD rate, 2025+</t>
   </si>
   <si>
-    <t>Refinancing scenarios (reference only — not used in base case)</t>
-  </si>
-  <si>
     <t>Refi swap rate, low</t>
   </si>
   <si>
@@ -496,9 +463,6 @@
     <t>Actual initial debt balance (EUR)</t>
   </si>
   <si>
-    <t>Lower of the three tests (market convention)</t>
-  </si>
-  <si>
     <t>Scale factor (actual / DSCR-sculpted)</t>
   </si>
   <si>
@@ -772,12 +736,6 @@
     <t>Capacity (MW)</t>
   </si>
   <si>
-    <t>600</t>
-  </si>
-  <si>
-    <t>752</t>
-  </si>
-  <si>
     <t>Gemini ~20% smaller</t>
   </si>
   <si>
@@ -796,21 +754,12 @@
     <t>Total project cost (EUR m)</t>
   </si>
   <si>
-    <t>2,800</t>
-  </si>
-  <si>
-    <t>1,491</t>
-  </si>
-  <si>
     <t>Gemini's cost reflects an earlier, higher-cost vintage</t>
   </si>
   <si>
     <t>Long-term debt facility (EUR m)</t>
   </si>
   <si>
-    <t>2,099</t>
-  </si>
-  <si>
     <t>920 (this model)</t>
   </si>
   <si>
@@ -841,9 +790,6 @@
     <t>Confirms multi-lender syndication is standard at this scale</t>
   </si>
   <si>
-    <t>Sources: Green Giraffe (Gemini transaction pages), EIB project database.</t>
-  </si>
-  <si>
     <t>Assumptions: all inputs (blue). Change a value and the model recalculates.</t>
   </si>
   <si>
@@ -862,9 +808,6 @@
     <t xml:space="preserve">     stream, discounted at the loan interest rate (a closed-form NPV, no circular</t>
   </si>
   <si>
-    <t>out slightly above the sizing target extra headroom for the lender.</t>
-  </si>
-  <si>
     <t>scenarios in Assumptions are shown for reference relevant only under an alternative,</t>
   </si>
   <si>
@@ -875,6 +818,45 @@
   </si>
   <si>
     <t>Key outputs</t>
+  </si>
+  <si>
+    <t>Debt is sized off the lowest of three tests:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2) Leverage cap: 70% of total project CAPEX.</t>
+  </si>
+  <si>
+    <t>CFADS for the sizing test excludes the interest tax shield (a conservative, standard</t>
+  </si>
+  <si>
+    <t>lender convention). The Cash Flow &amp; Waterfall tab computes actual tax with the interest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deduction, so realised DSCR normally comes out slightly above </t>
+  </si>
+  <si>
+    <t>the sizing target extra headroom for the lender.</t>
+  </si>
+  <si>
+    <t>Borssele 1 &amp; 2 Project Finance Debt Model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simplifications </t>
+  </si>
+  <si>
+    <t>Distribution lock-up traps cash rather than dynamically re-sculpting the</t>
+  </si>
+  <si>
+    <t>LLCR is shown at financial close, not re-tested every year.</t>
+  </si>
+  <si>
+    <t>Project 1's ex-ante lens.</t>
+  </si>
+  <si>
+    <t>Refinancing scenarios (reference only, not used in base case)</t>
+  </si>
+  <si>
+    <t>Lower of the three tests</t>
   </si>
 </sst>
 </file>
@@ -1072,7 +1054,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1227,6 +1209,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1501,7 +1489,7 @@
   <sheetData>
     <row r="2" spans="2:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
-        <v>0</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1509,147 +1497,147 @@
     </row>
     <row r="5" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="4" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="4" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="4" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="4" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="4" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="4" t="s">
-        <v>3</v>
+        <v>259</v>
       </c>
     </row>
     <row r="14" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="4" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="4" t="s">
-        <v>6</v>
+        <v>260</v>
       </c>
     </row>
     <row r="18" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="4" t="s">
-        <v>8</v>
+        <v>261</v>
       </c>
     </row>
     <row r="20" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="4" t="s">
-        <v>9</v>
+        <v>262</v>
       </c>
     </row>
     <row r="21" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="4" t="s">
-        <v>10</v>
+        <v>263</v>
       </c>
     </row>
     <row r="22" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="4" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
     </row>
     <row r="24" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="3" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="4" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B27" s="4" t="s">
-        <v>274</v>
+        <v>255</v>
       </c>
     </row>
     <row r="28" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" s="4" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="3" t="s">
-        <v>15</v>
+        <v>266</v>
       </c>
     </row>
     <row r="31" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B31" s="4" t="s">
-        <v>16</v>
+        <v>267</v>
       </c>
     </row>
     <row r="32" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B32" s="4" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
     </row>
     <row r="33" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B33" s="4" t="s">
-        <v>17</v>
+        <v>268</v>
       </c>
     </row>
     <row r="34" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B34" s="4" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B35" s="4" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B36" s="4" t="s">
-        <v>20</v>
+        <v>269</v>
       </c>
     </row>
   </sheetData>
@@ -1671,7 +1659,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1679,21 +1667,21 @@
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -1701,78 +1689,78 @@
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="B6" s="10">
         <v>752</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B7" s="13">
         <v>0.5</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B8" s="13">
         <v>0</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B9" s="13">
         <v>0.1</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B10" s="14">
         <f>_xlfn.NORM.INV(0.1,B7,B7*B9)</f>
         <v>0.43592242172276996</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -1780,64 +1768,64 @@
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B12" s="15">
         <v>1491</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B13" s="16">
         <f>B12*1000000</f>
         <v>1491000000</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B14" s="15">
         <v>42</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B15" s="13">
         <v>0.2</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -1845,49 +1833,49 @@
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B17" s="17">
         <v>9.59</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B18" s="15">
         <v>40350</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B19" s="13">
         <v>0.02</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
@@ -1895,77 +1883,77 @@
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B21" s="17">
         <v>72.7</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B22" s="17">
         <v>29</v>
       </c>
       <c r="C22" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" s="12" t="s">
         <v>51</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B23" s="18">
         <v>15</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B24" s="17">
         <v>30</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="B25" s="13">
         <v>-0.2</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -1973,176 +1961,176 @@
     </row>
     <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B27" s="19">
         <v>5.79E-3</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B28" s="20">
         <v>2.1999999999999999E-2</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B29" s="21">
         <f>B27+B28</f>
         <v>2.7789999999999999E-2</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="9" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B30" s="13">
         <v>0.7</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="9" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B31" s="18">
         <v>15</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="9" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B32" s="17">
         <v>1.3</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="9" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B33" s="17">
         <v>1.1000000000000001</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="9" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B34" s="17">
         <v>1.1499999999999999</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="9" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="B35" s="17">
         <v>1.2</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="9" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B36" s="17">
         <v>1.4</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="9" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="B37" s="13">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="9" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B38" s="18">
         <v>6</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="8" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
@@ -2150,105 +2138,105 @@
     </row>
     <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="9" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B40" s="15">
         <v>200000</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="9" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B41" s="13">
         <v>0.19</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="9" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B42" s="13">
         <v>0.25800000000000001</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="9" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="B43" s="15">
         <v>1000000</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="9" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B44" s="13">
         <v>0.3</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="9" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B45" s="13">
         <v>0.2</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="9" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B46" s="13">
         <v>0.245</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="8" t="s">
-        <v>106</v>
+        <v>270</v>
       </c>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
@@ -2256,130 +2244,130 @@
     </row>
     <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="9" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B48" s="20">
         <v>2.7E-2</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="9" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="B49" s="20">
         <v>3.3700000000000001E-2</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="9" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="B50" s="20">
         <v>3.44E-2</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="9" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="B51" s="20">
         <v>2.2499999999999999E-2</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="9" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="B52" s="20">
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="9" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="B53" s="20">
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="9" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="B54" s="21">
         <f>B48+B51</f>
         <v>4.9500000000000002E-2</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D54" s="12"/>
     </row>
     <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="9" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="B55" s="21">
         <f>B49+B52</f>
         <v>6.8700000000000011E-2</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D55" s="12"/>
     </row>
     <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="9" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="B56" s="21">
         <f>B50+B53</f>
         <v>7.9399999999999998E-2</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D56" s="12"/>
     </row>
     <row r="57" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="8" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
@@ -2387,30 +2375,30 @@
     </row>
     <row r="58" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="9" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="B58" s="18">
         <v>2021</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="9" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="B59" s="18">
         <v>25</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -2427,12 +2415,12 @@
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="44" customWidth="1"/>
-    <col min="4" max="16" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="16" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2440,25 +2428,25 @@
     </row>
     <row r="4" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
     </row>
     <row r="6" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="B6" s="16">
         <f>Assumptions!$B$6*Assumptions!$B$7*8760</f>
@@ -2467,7 +2455,7 @@
     </row>
     <row r="7" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="B7" s="16">
         <f>Assumptions!$B$13/Assumptions!$B$59</f>
@@ -2476,14 +2464,14 @@
     </row>
     <row r="8" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
     </row>
     <row r="9" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="22" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="B9" s="23">
         <v>1</v>
@@ -2533,7 +2521,7 @@
     </row>
     <row r="10" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="24" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="B10" s="25">
         <f>$B$6*(1-Assumptions!$B$8)^(B$9-1)</f>
@@ -2598,7 +2586,7 @@
     </row>
     <row r="11" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="24" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="B11" s="25">
         <f>B$10*Assumptions!$B$21</f>
@@ -2663,7 +2651,7 @@
     </row>
     <row r="12" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="24" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="B12" s="25">
         <f>(Assumptions!$B$17*(1+Assumptions!$B$19)^(B$9-1)*B$10)+(Assumptions!$B$18*(1+Assumptions!$B$19)^(B$9-1)*Assumptions!$B$6)</f>
@@ -2728,7 +2716,7 @@
     </row>
     <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="24" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="B13" s="25">
         <f t="shared" ref="B13:P13" si="0">B$11-B$12</f>
@@ -2793,7 +2781,7 @@
     </row>
     <row r="14" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="24" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="B14" s="25">
         <f t="shared" ref="B14:P14" si="1">B$13-$B$7</f>
@@ -2858,7 +2846,7 @@
     </row>
     <row r="15" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="24" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B15" s="25">
         <f>IF(B$14&lt;=0,0,IF(B$14&lt;=Assumptions!$B$40,B$14*Assumptions!$B$41,Assumptions!$B$40*Assumptions!$B$41+(B$14-Assumptions!$B$40)*Assumptions!$B$42))</f>
@@ -2923,7 +2911,7 @@
     </row>
     <row r="16" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="24" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="B16" s="25">
         <f t="shared" ref="B16:P16" si="2">B$13-B$15</f>
@@ -2988,7 +2976,7 @@
     </row>
     <row r="17" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="22" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="B17" s="26">
         <f>B$16/Assumptions!$B$32</f>
@@ -3053,62 +3041,62 @@
     </row>
     <row r="19" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
     </row>
     <row r="20" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="B20" s="16">
         <f>NPV(Assumptions!$B$29,B$17:P$17)</f>
         <v>1312320776.094835</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="B21" s="16">
         <f>Assumptions!$B$30*Assumptions!$B$13</f>
         <v>1043699999.9999999</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="B22" s="16">
         <f>NPV(Assumptions!$B$37,B$16:P$16)/Assumptions!$B$36</f>
         <v>919857405.80435824</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="28" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="B23" s="29">
         <f>MIN(B20,B21,B22)</f>
         <v>919857405.80435824</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>151</v>
+        <v>271</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="B24" s="30">
         <f>B23/B20</f>
@@ -3117,7 +3105,7 @@
     </row>
     <row r="25" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="B25" s="31">
         <f>Assumptions!$B$32/B24</f>
@@ -3126,7 +3114,7 @@
     </row>
     <row r="26" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="B26" s="32" t="str">
         <f>IF(B23=B20,"DSCR sculpting",IF(B23=B21,"Leverage cap","LLCR"))</f>
@@ -3135,14 +3123,14 @@
     </row>
     <row r="28" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="8" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
     </row>
     <row r="29" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="22" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="B29" s="26">
         <f t="shared" ref="B29:P29" si="3">B$17*$B$24</f>
@@ -3207,7 +3195,7 @@
     </row>
     <row r="31" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="28" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="B31" s="33">
         <f>NPV(Assumptions!$B$37,B$16:P$16)/B23</f>
@@ -3226,14 +3214,15 @@
   <dimension ref="A1:AB50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="1" max="1" width="34.5" customWidth="1"/>
+    <col min="2" max="2" width="4.33203125" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="28" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="34" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3241,7 +3230,7 @@
     </row>
     <row r="4" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="35" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="C4" s="36">
         <f>Assumptions!$B$58-1</f>
@@ -3350,7 +3339,7 @@
     </row>
     <row r="5" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="35" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="C5" s="37">
         <v>0</v>
@@ -3433,7 +3422,7 @@
     </row>
     <row r="8" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="38" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="C8" s="38"/>
       <c r="D8" s="38"/>
@@ -3464,7 +3453,7 @@
     </row>
     <row r="9" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="24" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="C9" s="39">
         <v>0</v>
@@ -3572,7 +3561,7 @@
     </row>
     <row r="10" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="24" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="C10" s="25">
         <v>0</v>
@@ -3680,7 +3669,7 @@
     </row>
     <row r="11" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="38" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="C11" s="38"/>
       <c r="D11" s="38"/>
@@ -3711,7 +3700,7 @@
     </row>
     <row r="12" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="24" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C12" s="40">
         <v>0</v>
@@ -3819,7 +3808,7 @@
     </row>
     <row r="13" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="24" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C13" s="40">
         <v>0</v>
@@ -3917,7 +3906,7 @@
     </row>
     <row r="14" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="24" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C14" s="40">
         <v>0</v>
@@ -4025,7 +4014,7 @@
     </row>
     <row r="15" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="24" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="C15" s="41">
         <v>0</v>
@@ -4133,7 +4122,7 @@
     </row>
     <row r="16" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="38" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C16" s="38"/>
       <c r="D16" s="38"/>
@@ -4164,7 +4153,7 @@
     </row>
     <row r="17" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="24" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="C17" s="41">
         <v>0</v>
@@ -4272,7 +4261,7 @@
     </row>
     <row r="18" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="24" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="C18" s="41">
         <v>0</v>
@@ -4380,7 +4369,7 @@
     </row>
     <row r="19" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="24" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="C19" s="41">
         <v>0</v>
@@ -4488,7 +4477,7 @@
     </row>
     <row r="20" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="38" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="C20" s="38"/>
       <c r="D20" s="38"/>
@@ -4519,7 +4508,7 @@
     </row>
     <row r="21" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="24" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="C21" s="41">
         <v>0</v>
@@ -4627,7 +4616,7 @@
     </row>
     <row r="22" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="24" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="C22" s="41">
         <v>0</v>
@@ -4735,7 +4724,7 @@
     </row>
     <row r="23" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="38" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="C23" s="38"/>
       <c r="D23" s="38"/>
@@ -4766,7 +4755,7 @@
     </row>
     <row r="24" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="24" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C24" s="41">
         <v>0</v>
@@ -4864,7 +4853,7 @@
     </row>
     <row r="25" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="24" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C25" s="41">
         <v>0</v>
@@ -4972,7 +4961,7 @@
     </row>
     <row r="26" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="24" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="C26" s="41">
         <v>0</v>
@@ -5070,7 +5059,7 @@
     </row>
     <row r="27" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="24" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="C27" s="41">
         <v>0</v>
@@ -5178,7 +5167,7 @@
     </row>
     <row r="28" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="24" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="C28" s="41">
         <v>0</v>
@@ -5286,7 +5275,7 @@
     </row>
     <row r="29" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="38" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="C29" s="38"/>
       <c r="D29" s="38"/>
@@ -5317,7 +5306,7 @@
     </row>
     <row r="30" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="24" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="C30" s="42">
         <v>0</v>
@@ -5425,7 +5414,7 @@
     </row>
     <row r="31" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="24" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="C31" s="41">
         <v>0</v>
@@ -5533,7 +5522,7 @@
     </row>
     <row r="32" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="24" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="C32" s="41">
         <v>0</v>
@@ -5641,7 +5630,7 @@
     </row>
     <row r="33" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="24" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="C33" s="41">
         <v>0</v>
@@ -5749,7 +5738,7 @@
     </row>
     <row r="34" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="24" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="C34" s="41">
         <v>0</v>
@@ -5857,7 +5846,7 @@
     </row>
     <row r="35" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="38" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="C35" s="38"/>
       <c r="D35" s="38"/>
@@ -5888,7 +5877,7 @@
     </row>
     <row r="36" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="24" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="C36" s="41">
         <f>-Assumptions!$B$13</f>
@@ -5972,7 +5961,7 @@
     </row>
     <row r="37" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="24" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="C37" s="41">
         <f>'Debt Sizing'!$B$23</f>
@@ -6056,7 +6045,7 @@
     </row>
     <row r="38" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="24" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="C38" s="41">
         <f>-(C36+C37)+C41</f>
@@ -6140,7 +6129,7 @@
     </row>
     <row r="39" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="24" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="C39" s="41">
         <v>0</v>
@@ -6248,7 +6237,7 @@
     </row>
     <row r="40" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="24" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="C40" s="41">
         <v>0</v>
@@ -6356,7 +6345,7 @@
     </row>
     <row r="41" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="24" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="C41" s="41">
         <f>'Debt Sizing'!$B$29*Assumptions!$B$38/12</f>
@@ -6464,7 +6453,7 @@
     </row>
     <row r="42" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="24" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="C42" s="41">
         <v>0</v>
@@ -6572,7 +6561,7 @@
     </row>
     <row r="43" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="24" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="C43" s="41">
         <v>0</v>
@@ -6680,10 +6669,10 @@
     </row>
     <row r="44" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="24" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="C44" s="41" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="D44" s="43">
         <f t="shared" ref="D44:AB44" si="13">IF(D$26=0,"n/a",D$39/D$26)</f>
@@ -6788,10 +6777,10 @@
     </row>
     <row r="45" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="24" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="C45" s="41" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="D45" s="43">
         <f t="shared" ref="D45:AA45" si="14">IF(E$26=0,"n/a",E$39/E$26)</f>
@@ -6890,15 +6879,15 @@
         <v>n/a</v>
       </c>
       <c r="AB45" s="41" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
     </row>
     <row r="46" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="24" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="C46" s="41" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="D46" s="41" t="str">
         <f>IF(D$26=0,"n/a (unlevered)",IF(AND(D$44&gt;=Assumptions!$B$35,IFERROR(D$45&gt;=Assumptions!$B$35,TRUE())),"PASS","FAIL"))</f>
@@ -7003,7 +6992,7 @@
     </row>
     <row r="47" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="24" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="C47" s="41">
         <v>0</v>
@@ -7111,7 +7100,7 @@
     </row>
     <row r="48" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="24" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="C48" s="41">
         <v>0</v>
@@ -7219,7 +7208,7 @@
     </row>
     <row r="49" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="24" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="C49" s="41">
         <v>0</v>
@@ -7303,7 +7292,7 @@
     </row>
     <row r="50" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="24" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="C50" s="41">
         <f>C36+C37+C38-C41</f>
@@ -7427,7 +7416,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="34" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7435,7 +7424,7 @@
     </row>
     <row r="4" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="22" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="B4" s="23">
         <v>1</v>
@@ -7485,7 +7474,7 @@
     </row>
     <row r="5" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="44" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="B5" s="45">
         <f>'Cash Flow &amp; Waterfall'!$D$26</f>
@@ -7550,7 +7539,7 @@
     </row>
     <row r="7" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="38" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="B7" s="38"/>
       <c r="C7" s="38"/>
@@ -7570,7 +7559,7 @@
     </row>
     <row r="8" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="24" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="B8" s="25">
         <f>Assumptions!$B$6*Assumptions!$B$7*8760*(1-Assumptions!$B$8)^(B$4-1)</f>
@@ -7635,7 +7624,7 @@
     </row>
     <row r="9" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="24" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="B9" s="43">
         <f>Assumptions!$B$24</f>
@@ -7700,7 +7689,7 @@
     </row>
     <row r="10" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="24" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="B10" s="43">
         <f>B$9+MAX(0,Assumptions!$B$21-MAX(B$9,Assumptions!$B$22))</f>
@@ -7765,7 +7754,7 @@
     </row>
     <row r="11" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="24" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="B11" s="25">
         <f t="shared" ref="B11:P11" si="0">B$8*B$10</f>
@@ -7830,7 +7819,7 @@
     </row>
     <row r="12" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="24" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="B12" s="25">
         <f>(Assumptions!$B$17*(1+Assumptions!$B$19)^(B$4-1)*B$8)+(Assumptions!$B$18*(1+Assumptions!$B$19)^(B$4-1)*Assumptions!$B$6)</f>
@@ -7895,7 +7884,7 @@
     </row>
     <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="24" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="B13" s="25">
         <f t="shared" ref="B13:P13" si="1">B$11-B$12</f>
@@ -7960,7 +7949,7 @@
     </row>
     <row r="14" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="24" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="B14" s="25">
         <f>-MAX(0,(B$13-Assumptions!$B$13/Assumptions!$B$59)*Assumptions!$B$42)</f>
@@ -8025,7 +8014,7 @@
     </row>
     <row r="15" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="22" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="B15" s="26">
         <f t="shared" ref="B15:P15" si="2">B$13+B$14</f>
@@ -8090,7 +8079,7 @@
     </row>
     <row r="16" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="22" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="B16" s="46">
         <f t="shared" ref="B16:P16" si="3">B$15/B$5</f>
@@ -8155,7 +8144,7 @@
     </row>
     <row r="17" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="47" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="B17" s="48">
         <f>MIN(B16:P16)</f>
@@ -8176,7 +8165,7 @@
     </row>
     <row r="19" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="38" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="B19" s="38"/>
       <c r="C19" s="38"/>
@@ -8196,7 +8185,7 @@
     </row>
     <row r="20" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="24" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="B20" s="25">
         <f>Assumptions!$B$6*Assumptions!$B$10*8760*(1-Assumptions!$B$8)^(B$4-1)</f>
@@ -8261,7 +8250,7 @@
     </row>
     <row r="21" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="24" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="B21" s="43">
         <f>Assumptions!$B$24</f>
@@ -8326,7 +8315,7 @@
     </row>
     <row r="22" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="24" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="B22" s="43">
         <f>B$21+MAX(0,Assumptions!$B$21-MAX(B$21,Assumptions!$B$22))</f>
@@ -8391,7 +8380,7 @@
     </row>
     <row r="23" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="24" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="B23" s="25">
         <f t="shared" ref="B23:P23" si="4">B$20*B$22</f>
@@ -8456,7 +8445,7 @@
     </row>
     <row r="24" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="24" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="B24" s="25">
         <f>(Assumptions!$B$17*(1+Assumptions!$B$19)^(B$4-1)*B$20)+(Assumptions!$B$18*(1+Assumptions!$B$19)^(B$4-1)*Assumptions!$B$6)</f>
@@ -8521,7 +8510,7 @@
     </row>
     <row r="25" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="24" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="B25" s="25">
         <f t="shared" ref="B25:P25" si="5">B$23-B$24</f>
@@ -8586,7 +8575,7 @@
     </row>
     <row r="26" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="24" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="B26" s="25">
         <f>-MAX(0,(B$25-Assumptions!$B$13/Assumptions!$B$59)*Assumptions!$B$42)</f>
@@ -8651,7 +8640,7 @@
     </row>
     <row r="27" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="22" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="B27" s="26">
         <f t="shared" ref="B27:P27" si="6">B$25+B$26</f>
@@ -8716,7 +8705,7 @@
     </row>
     <row r="28" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="22" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="B28" s="46">
         <f t="shared" ref="B28:P28" si="7">B$27/B$5</f>
@@ -8781,7 +8770,7 @@
     </row>
     <row r="29" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="47" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="B29" s="48">
         <f>MIN(B28:P28)</f>
@@ -8802,7 +8791,7 @@
     </row>
     <row r="31" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="38" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="B31" s="38"/>
       <c r="C31" s="38"/>
@@ -8822,7 +8811,7 @@
     </row>
     <row r="32" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="24" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="B32" s="25">
         <f>Assumptions!$B$6*Assumptions!$B$7*8760*(1-Assumptions!$B$8)^(B$4-1)</f>
@@ -8887,7 +8876,7 @@
     </row>
     <row r="33" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="24" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="B33" s="43">
         <f>Assumptions!$B$24*(1+Assumptions!$B$25)</f>
@@ -8952,7 +8941,7 @@
     </row>
     <row r="34" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="24" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="B34" s="43">
         <f>B$33+MAX(0,Assumptions!$B$21-MAX(B$33,Assumptions!$B$22))</f>
@@ -9017,7 +9006,7 @@
     </row>
     <row r="35" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="24" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="B35" s="25">
         <f t="shared" ref="B35:P35" si="8">B$32*B$34</f>
@@ -9082,7 +9071,7 @@
     </row>
     <row r="36" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="24" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="B36" s="25">
         <f>(Assumptions!$B$17*(1+Assumptions!$B$19)^(B$4-1)*B$32)+(Assumptions!$B$18*(1+Assumptions!$B$19)^(B$4-1)*Assumptions!$B$6)</f>
@@ -9147,7 +9136,7 @@
     </row>
     <row r="37" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="24" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="B37" s="25">
         <f t="shared" ref="B37:P37" si="9">B$35-B$36</f>
@@ -9212,7 +9201,7 @@
     </row>
     <row r="38" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="24" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="B38" s="25">
         <f>-MAX(0,(B$37-Assumptions!$B$13/Assumptions!$B$59)*Assumptions!$B$42)</f>
@@ -9277,7 +9266,7 @@
     </row>
     <row r="39" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="22" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="B39" s="26">
         <f t="shared" ref="B39:P39" si="10">B$37+B$38</f>
@@ -9342,7 +9331,7 @@
     </row>
     <row r="40" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="22" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="B40" s="46">
         <f t="shared" ref="B40:P40" si="11">B$39/B$5</f>
@@ -9407,7 +9396,7 @@
     </row>
     <row r="41" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="47" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="B41" s="48">
         <f>MIN(B40:P40)</f>
@@ -9428,7 +9417,7 @@
     </row>
     <row r="43" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="38" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="B43" s="38"/>
       <c r="C43" s="38"/>
@@ -9448,7 +9437,7 @@
     </row>
     <row r="44" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="24" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="B44" s="25">
         <f>Assumptions!$B$6*Assumptions!$B$10*8760*(1-Assumptions!$B$8)^(B$4-1)</f>
@@ -9513,7 +9502,7 @@
     </row>
     <row r="45" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="24" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="B45" s="43">
         <f>Assumptions!$B$24*(1+Assumptions!$B$25)</f>
@@ -9578,7 +9567,7 @@
     </row>
     <row r="46" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="24" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="B46" s="43">
         <f>B$45+MAX(0,Assumptions!$B$21-MAX(B$45,Assumptions!$B$22))</f>
@@ -9643,7 +9632,7 @@
     </row>
     <row r="47" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="24" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="B47" s="25">
         <f t="shared" ref="B47:P47" si="12">B$44*B$46</f>
@@ -9708,7 +9697,7 @@
     </row>
     <row r="48" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="24" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="B48" s="25">
         <f>(Assumptions!$B$17*(1+Assumptions!$B$19)^(B$4-1)*B$44)+(Assumptions!$B$18*(1+Assumptions!$B$19)^(B$4-1)*Assumptions!$B$6)</f>
@@ -9773,7 +9762,7 @@
     </row>
     <row r="49" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="24" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="B49" s="25">
         <f t="shared" ref="B49:P49" si="13">B$47-B$48</f>
@@ -9838,7 +9827,7 @@
     </row>
     <row r="50" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="24" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="B50" s="25">
         <f>-MAX(0,(B$49-Assumptions!$B$13/Assumptions!$B$59)*Assumptions!$B$42)</f>
@@ -9903,7 +9892,7 @@
     </row>
     <row r="51" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="22" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="B51" s="26">
         <f t="shared" ref="B51:P51" si="14">B$49+B$50</f>
@@ -9968,7 +9957,7 @@
     </row>
     <row r="52" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="22" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="B52" s="46">
         <f t="shared" ref="B52:P52" si="15">B$51/B$5</f>
@@ -10033,7 +10022,7 @@
     </row>
     <row r="53" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="47" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="B53" s="48">
         <f>MIN(B52:P52)</f>
@@ -10054,14 +10043,14 @@
     </row>
     <row r="55" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="38" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="B55" s="38"/>
       <c r="C55" s="38"/>
     </row>
     <row r="56" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="24" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="B56" s="25">
         <f>Assumptions!$B$13*Assumptions!$B$15</f>
@@ -10070,10 +10059,10 @@
     </row>
     <row r="57" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="24" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="B57" s="44" t="s">
-        <v>276</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -10088,13 +10077,14 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="3" width="18" customWidth="1"/>
+    <col min="2" max="2" width="28.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="19" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -10102,7 +10092,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -10110,79 +10100,79 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="B6" s="51">
         <f>'Debt Sizing'!$B$23/1000000</f>
         <v>919.85740580435822</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="B7" s="52" t="str">
         <f>'Debt Sizing'!$B$26</f>
         <v>LLCR</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="B8" s="53">
         <f>'Debt Sizing'!$B$23/Assumptions!$B$13</f>
         <v>0.61693990999621617</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="B9" s="54">
         <f>'Debt Sizing'!$B$25</f>
         <v>1.8546537736808018</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B10" s="54">
         <f>'Debt Sizing'!$B$31</f>
         <v>1.4</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -10190,21 +10180,21 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="B14" s="33">
         <f>'Stress Tests'!$B$17</f>
@@ -10215,12 +10205,12 @@
         <v>Clears</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="B15" s="33">
         <f>'Stress Tests'!$B$29</f>
@@ -10231,12 +10221,12 @@
         <v>Clears</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="B16" s="33">
         <f>'Stress Tests'!$B$41</f>
@@ -10247,12 +10237,12 @@
         <v>Clears</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="B17" s="33">
         <f>'Stress Tests'!$B$53</f>
@@ -10263,12 +10253,12 @@
         <v>Clears</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -10276,106 +10266,104 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="B21" s="32" t="s">
-        <v>243</v>
-      </c>
-      <c r="C21" s="55" t="s">
-        <v>244</v>
+        <v>230</v>
+      </c>
+      <c r="B21" s="57">
+        <v>600</v>
+      </c>
+      <c r="C21" s="58">
+        <v>752</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="B22" s="32" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="C22" s="55" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="B23" s="32" t="s">
-        <v>251</v>
-      </c>
-      <c r="C23" s="55" t="s">
-        <v>252</v>
+        <v>236</v>
+      </c>
+      <c r="B23" s="57">
+        <v>2.8</v>
+      </c>
+      <c r="C23" s="58">
+        <v>1.4910000000000001</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="B24" s="32" t="s">
-        <v>255</v>
+        <v>238</v>
+      </c>
+      <c r="B24" s="57">
+        <v>2.0990000000000002</v>
       </c>
       <c r="C24" s="55" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="s">
-        <v>258</v>
+        <v>241</v>
       </c>
       <c r="B25" s="32" t="s">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="C25" s="55" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="B26" s="32" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="C26" s="55" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="26" x14ac:dyDescent="0.2">
-      <c r="A28" s="56" t="s">
-        <v>266</v>
-      </c>
+        <v>248</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="56"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
